--- a/cds/mm_turkey-5year-cds.xlsx
+++ b/cds/mm_turkey-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="669">
   <si>
     <t>Date</t>
   </si>
@@ -2007,6 +2007,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -2356,7 +2371,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B663"/>
+  <dimension ref="A1:B668"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7661,6 +7676,46 @@
       </c>
       <c r="B663" s="3">
         <v>243.615</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B664" s="3">
+        <v>266.5708</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="B665" s="3">
+        <v>289.2852</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B666" s="3">
+        <v>304.3989</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B667" s="3">
+        <v>288.6055</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B668" s="3">
+        <v>239.931</v>
       </c>
     </row>
   </sheetData>
